--- a/output/topology_excel/898.xlsx
+++ b/output/topology_excel/898.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,57 +490,75 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1846</v>
+        <v>28050</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>46</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>54340</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2145</v>
+        <v>473052</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>58</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -533,255 +566,336 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>23290</v>
+      </c>
+      <c r="D4" t="n">
         <v>13</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1624</v>
+        <v>473052</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>28050</v>
+      </c>
+      <c r="D5" t="n">
         <v>13</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>190</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5320</v>
+        <v>473052</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>43</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>23100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>48</v>
+      </c>
+      <c r="J6" t="n">
         <v>13</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D7" t="n">
         <v>13</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F7" t="n">
-        <v>137</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3836</v>
+        <v>473052</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>228</v>
+      </c>
+      <c r="J7" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>473052</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3836</v>
+        <v>19740</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>64</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>473052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F9" t="n">
-        <v>165</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9600</v>
+        <v>23100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>49</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>133452</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1872</v>
+        <v>473052</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>63270</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>15</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F11" t="n">
-        <v>165</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2145</v>
+        <v>695873</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>85</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>63270</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7352</v>
+        <v>32912</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -794,255 +908,336 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>423</v>
-      </c>
-      <c r="G13" t="n">
-        <v>32657</v>
+        <v>22040</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2048</v>
+        <v>130962</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>82</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4480</v>
+        <v>54340</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>76</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1760</v>
+        <v>105481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>87</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>28050</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>96</v>
+      </c>
+      <c r="J17" t="n">
         <v>13</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>154</v>
-      </c>
-      <c r="G17" t="n">
-        <v>27296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>58608</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1360</v>
+        <v>54340</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>23290</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>122</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17711</v>
+        <v>28050</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>73</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>28050</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1050</v>
+        <v>473052</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>166</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2324</v>
+        <v>133452</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>84</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -1055,23 +1250,32 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1200</v>
+        <v>19740</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>76</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1084,168 +1288,222 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>116</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1856</v>
+        <v>23100</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>96</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>122298</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>984</v>
+        <v>473052</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>95</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>473052</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>386</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4632</v>
+        <v>23100</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>91</v>
+      </c>
+      <c r="J25" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>63270</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1216</v>
+        <v>695873</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>88</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" t="inlineStr">
+        <v>63270</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F27" t="n">
-        <v>127</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1905</v>
+        <v>32912</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>166</v>
+      </c>
+      <c r="J27" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>63270</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1218</v>
+        <v>22040</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>190</v>
+      </c>
+      <c r="J28" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -1258,81 +1516,108 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" t="inlineStr">
+        <v>695873</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F29" t="n">
-        <v>313</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4382</v>
+        <v>130962</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>311</v>
+      </c>
+      <c r="J29" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1050</v>
+        <v>22040</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>143</v>
+      </c>
+      <c r="J30" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1168</v>
+        <v>32912</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>220</v>
+      </c>
+      <c r="J31" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="32">
@@ -1345,23 +1630,32 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1176</v>
+        <v>58608</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>220</v>
+      </c>
+      <c r="J32" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="33">
@@ -1374,23 +1668,32 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" t="inlineStr">
+        <v>695873</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F33" t="n">
-        <v>102</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5744</v>
+        <v>105481</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>313</v>
+      </c>
+      <c r="J33" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1403,23 +1706,32 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>988</v>
+        <v>54340</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>143</v>
+      </c>
+      <c r="J34" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -1432,139 +1744,184 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D35" t="n">
+        <v>9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>141</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1833</v>
+        <v>23290</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>137</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D36" t="n">
         <v>13</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2185</v>
+        <v>473052</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>713</v>
+      </c>
+      <c r="J36" t="n">
+        <v>460</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>561</v>
-      </c>
-      <c r="G37" t="n">
-        <v>12903</v>
+        <v>28050</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>183</v>
+      </c>
+      <c r="J37" t="n">
+        <v>178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F38" t="n">
+        <v>133452</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>89</v>
+      </c>
+      <c r="J38" t="n">
         <v>14</v>
-      </c>
-      <c r="G38" t="n">
-        <v>8092</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D39" t="n">
+        <v>14</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F39" t="n">
-        <v>190</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2660</v>
+        <v>19740</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>154</v>
+      </c>
+      <c r="J39" t="n">
+        <v>153</v>
       </c>
     </row>
     <row r="40">
@@ -1577,139 +1934,184 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>695873</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>71</v>
-      </c>
-      <c r="G40" t="n">
-        <v>7469</v>
+        <v>23100</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>165</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>130962</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>32</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2464</v>
+        <v>105481</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>337</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>32912</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>137</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1781</v>
+        <v>22040</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>116</v>
+      </c>
+      <c r="J42" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>32912</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>337</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4044</v>
+        <v>58608</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>176</v>
+      </c>
+      <c r="J43" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>22040</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>6</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F44" t="n">
-        <v>176</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2816</v>
+        <v>54340</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>134</v>
+      </c>
+      <c r="J44" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="45">
@@ -1722,23 +2124,32 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>58608</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>59</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1652</v>
+        <v>54340</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>286</v>
+      </c>
+      <c r="J45" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -1751,110 +2162,526 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>13</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>58608</v>
+      </c>
+      <c r="D46" t="n">
+        <v>12</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>94</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2632</v>
+        <v>122298</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>59</v>
+      </c>
+      <c r="J46" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>58608</v>
+      </c>
+      <c r="D47" t="n">
+        <v>13</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>337</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5055</v>
+        <v>473052</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>94</v>
+      </c>
+      <c r="J47" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>105481</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>63</v>
-      </c>
-      <c r="G48" t="n">
-        <v>8442</v>
+        <v>133452</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>337</v>
+      </c>
+      <c r="J48" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>54340</v>
+      </c>
+      <c r="D49" t="n">
+        <v>9</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>23290</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>170</v>
+      </c>
+      <c r="J49" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>54340</v>
+      </c>
+      <c r="D50" t="n">
+        <v>13</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>473052</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>190</v>
+      </c>
+      <c r="J50" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>23290</v>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>28050</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>170</v>
+      </c>
+      <c r="J51" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>23290</v>
+      </c>
+      <c r="D52" t="n">
+        <v>13</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>473052</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>137</v>
+      </c>
+      <c r="J52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>28050</v>
+      </c>
+      <c r="D53" t="n">
+        <v>13</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>473052</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>277</v>
+      </c>
+      <c r="J53" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>11</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C54" t="n">
+        <v>133452</v>
+      </c>
+      <c r="D54" t="n">
         <v>15</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
+      <c r="F54" t="n">
+        <v>23100</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
         <v>140</v>
       </c>
-      <c r="G49" t="n">
-        <v>1960</v>
+      <c r="J54" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>133452</v>
+      </c>
+      <c r="D55" t="n">
+        <v>13</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>473052</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>122</v>
+      </c>
+      <c r="J55" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>12</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>122298</v>
+      </c>
+      <c r="D56" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>473052</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>561</v>
+      </c>
+      <c r="J56" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>473052</v>
+      </c>
+      <c r="D57" t="n">
+        <v>14</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>19740</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>141</v>
+      </c>
+      <c r="J57" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>13</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>473052</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>23100</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>147</v>
+      </c>
+      <c r="J58" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>14</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>19740</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>23100</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>140</v>
+      </c>
+      <c r="J59" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/898.xlsx
+++ b/output/topology_excel/898.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,27 +482,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>63270</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Living Room</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="F2" t="n">
         <v>695873</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>28050</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>门</t>
@@ -512,34 +512,34 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>63270</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>54340</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
       <c r="F3" t="n">
-        <v>473052</v>
+        <v>32912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,34 +550,34 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23290</v>
+        <v>695873</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>473052</v>
+        <v>22040</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -588,34 +588,34 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28050</v>
+        <v>695873</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>473052</v>
+        <v>130962</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -626,10 +626,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="J5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -645,15 +645,15 @@
         <v>695873</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23100</v>
+        <v>54340</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -664,10 +664,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -683,15 +683,15 @@
         <v>695873</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>473052</v>
+        <v>105481</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -699,75 +699,75 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>228</v>
+        <v>87</v>
       </c>
       <c r="J7" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>695873</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>28050</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>96</v>
+      </c>
+      <c r="J8" t="n">
         <v>13</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>473052</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>19740</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>64</v>
-      </c>
-      <c r="J8" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>473052</v>
+        <v>58608</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23100</v>
+        <v>54340</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -778,34 +778,34 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="J9" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>133452</v>
+        <v>23290</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>473052</v>
+        <v>28050</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -816,83 +816,83 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="J10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63270</v>
+        <v>28050</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>695873</v>
+        <v>473052</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>63270</v>
+        <v>695873</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32912</v>
+        <v>133452</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J12" t="n">
         <v>14</v>
@@ -911,29 +911,29 @@
         <v>695873</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>22040</v>
+        <v>19740</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -949,105 +949,105 @@
         <v>695873</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>130962</v>
+        <v>23100</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>695873</v>
+        <v>122298</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54340</v>
+        <v>473052</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>695873</v>
+        <v>473052</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>105481</v>
+        <v>23100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1082,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="J17" t="n">
         <v>13</v>
@@ -1090,26 +1090,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58608</v>
+        <v>54340</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54340</v>
+        <v>473052</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1139,15 +1139,15 @@
         <v>23290</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>28050</v>
+        <v>473052</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1196,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="J20" t="n">
         <v>28</v>
@@ -1215,15 +1215,15 @@
         <v>695873</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>133452</v>
+        <v>23100</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -1253,15 +1253,15 @@
         <v>695873</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19740</v>
+        <v>473052</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1269,37 +1269,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>695873</v>
+        <v>473052</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>23100</v>
+        <v>19740</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,34 +1310,34 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>122298</v>
+        <v>473052</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>473052</v>
+        <v>23100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,35 +1348,35 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>133452</v>
+      </c>
+      <c r="D25" t="n">
         <v>13</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="F25" t="n">
         <v>473052</v>
       </c>
-      <c r="D25" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>23100</v>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>窗</t>
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="J25" t="n">
         <v>32</v>
@@ -1614,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="J31" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
@@ -1652,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="J32" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1785,15 +1785,15 @@
         <v>695873</v>
       </c>
       <c r="D36" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>473052</v>
+        <v>28050</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>713</v>
+        <v>183</v>
       </c>
       <c r="J36" t="n">
-        <v>460</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37">
@@ -1823,15 +1823,15 @@
         <v>695873</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>28050</v>
+        <v>133452</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="J37" t="n">
-        <v>178</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -1861,15 +1861,15 @@
         <v>695873</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>133452</v>
+        <v>473052</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>89</v>
+        <v>385</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>22040</v>
+        <v>58608</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
@@ -2108,10 +2108,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>134</v>
+        <v>286</v>
       </c>
       <c r="J44" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -2127,15 +2127,15 @@
         <v>58608</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>54340</v>
+        <v>122298</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>286</v>
+        <v>59</v>
       </c>
       <c r="J45" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -2165,15 +2165,15 @@
         <v>58608</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>122298</v>
+        <v>473052</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="J46" t="n">
         <v>28</v>
@@ -2192,26 +2192,26 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>58608</v>
+        <v>105481</v>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>473052</v>
+        <v>133452</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2222,34 +2222,34 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="J47" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>105481</v>
+        <v>54340</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>133452</v>
+        <v>23290</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>337</v>
+        <v>170</v>
       </c>
       <c r="J48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -2279,15 +2279,15 @@
         <v>54340</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>23290</v>
+        <v>473052</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2298,15 +2298,15 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="J49" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2314,18 +2314,18 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>54340</v>
+        <v>23290</v>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>473052</v>
+        <v>28050</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="J50" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
@@ -2355,15 +2355,15 @@
         <v>23290</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>28050</v>
+        <v>473052</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2374,23 +2374,23 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="J51" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>23290</v>
+        <v>28050</v>
       </c>
       <c r="D52" t="n">
         <v>13</v>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J52" t="n">
         <v>28</v>
@@ -2420,26 +2420,26 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>133452</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>28050</v>
-      </c>
-      <c r="D53" t="n">
-        <v>13</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
       <c r="F53" t="n">
-        <v>473052</v>
+        <v>23100</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2450,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>277</v>
+        <v>140</v>
       </c>
       <c r="J53" t="n">
-        <v>165</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
@@ -2469,15 +2469,15 @@
         <v>133452</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>23100</v>
+        <v>473052</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2488,23 +2488,23 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="J54" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>133452</v>
+        <v>122298</v>
       </c>
       <c r="D55" t="n">
         <v>13</v>
@@ -2526,34 +2526,34 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>122</v>
+        <v>561</v>
       </c>
       <c r="J55" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>122298</v>
+        <v>473052</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>473052</v>
+        <v>19740</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="J56" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
@@ -2583,15 +2583,15 @@
         <v>473052</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>19740</v>
+        <v>23100</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J57" t="n">
         <v>32</v>
@@ -2610,15 +2610,15 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>473052</v>
+        <v>19740</v>
       </c>
       <c r="D58" t="n">
         <v>15</v>
@@ -2640,47 +2640,9 @@
         <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J58" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>14</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>19740</v>
-      </c>
-      <c r="D59" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>23100</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>140</v>
-      </c>
-      <c r="J59" t="n">
         <v>13</v>
       </c>
     </row>

--- a/output/topology_excel/898.xlsx
+++ b/output/topology_excel/898.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
         <v>14</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>166</v>
+        <v>336</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
@@ -1037,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="F29" t="n">
-        <v>99</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F30" t="n">
-        <v>130</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -1103,7 +1103,7 @@
         <v>2</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1125,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>313</v>
+        <v>87</v>
       </c>
       <c r="F33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>143</v>
+        <v>337</v>
       </c>
       <c r="F34" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>183</v>
+        <v>337</v>
       </c>
       <c r="F36" t="n">
-        <v>178</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,15 +1268,15 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>385</v>
+        <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>249</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
         <v>14</v>
@@ -1290,15 +1290,15 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="F39" t="n">
-        <v>153</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B40" t="n">
         <v>15</v>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>337</v>
+        <v>166</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="F42" t="n">
         <v>14</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>286</v>
+        <v>140</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,40 +1422,40 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B46" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>165</v>
+      </c>
+      <c r="F46" t="n">
         <v>13</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>94</v>
-      </c>
-      <c r="F46" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>337</v>
+        <v>165</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="F49" t="n">
         <v>28</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="F50" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B51" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F52" t="n">
-        <v>28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="F53" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="F54" t="n">
         <v>32</v>
@@ -1631,7 +1631,7 @@
         <v>12</v>
       </c>
       <c r="B55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,19 +1642,19 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>561</v>
+        <v>286</v>
       </c>
       <c r="F55" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>12</v>
+      </c>
+      <c r="B56" t="n">
         <v>13</v>
       </c>
-      <c r="B56" t="n">
-        <v>14</v>
-      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,32 +1686,296 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="F57" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" t="n">
+        <v>14</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>561</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>14</v>
+      </c>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>190</v>
+      </c>
+      <c r="F59" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" t="n">
+        <v>18</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>137</v>
+      </c>
+      <c r="F60" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
         <v>15</v>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>140</v>
-      </c>
-      <c r="F58" t="n">
+      <c r="B61" t="n">
+        <v>16</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>77</v>
+      </c>
+      <c r="F61" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" t="n">
+        <v>17</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>143</v>
+      </c>
+      <c r="F62" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>15</v>
+      </c>
+      <c r="B63" t="n">
+        <v>18</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>137</v>
+      </c>
+      <c r="F63" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>17</v>
+      </c>
+      <c r="B64" t="n">
+        <v>18</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>170</v>
+      </c>
+      <c r="F64" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>161</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>68</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B67" t="n">
+        <v>15</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>114</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="n">
+        <v>15</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>74</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>124</v>
+      </c>
+      <c r="F70" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/898.xlsx
+++ b/output/topology_excel/898.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>12</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>14</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>14</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>28</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>14</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>23</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>32</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>13</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>28</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>28</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>28</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>13</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,7 +963,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>228</v>
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>97</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>32</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>32</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>32</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1007,8 +1065,10 @@
         <v>310</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,13 +1083,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>336</v>
+        <v>63</v>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>150</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1053,6 +1119,8 @@
       <c r="F28" t="n">
         <v>13</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1067,13 +1135,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>385</v>
+        <v>217</v>
       </c>
       <c r="F29" t="n">
-        <v>249</v>
+        <v>33</v>
+      </c>
+      <c r="G29" t="n">
+        <v>352</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1097,6 +1171,8 @@
       <c r="F30" t="n">
         <v>13</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1195,8 @@
       <c r="F31" t="n">
         <v>13</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1219,8 @@
       <c r="F32" t="n">
         <v>12</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1243,8 @@
       <c r="F33" t="n">
         <v>12</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1267,8 @@
       <c r="F34" t="n">
         <v>12</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1291,8 @@
       <c r="F35" t="n">
         <v>14</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1315,8 @@
       <c r="F36" t="n">
         <v>15</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1339,8 @@
       <c r="F37" t="n">
         <v>14</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1363,8 @@
       <c r="F38" t="n">
         <v>14</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1387,8 @@
       <c r="F39" t="n">
         <v>32</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1411,8 @@
       <c r="F40" t="n">
         <v>16</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1435,8 @@
       <c r="F41" t="n">
         <v>14</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1459,8 @@
       <c r="F42" t="n">
         <v>14</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1483,8 @@
       <c r="F43" t="n">
         <v>13</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1507,8 @@
       <c r="F44" t="n">
         <v>13</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1531,8 @@
       <c r="F45" t="n">
         <v>32</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1555,8 @@
       <c r="F46" t="n">
         <v>13</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1579,8 @@
       <c r="F47" t="n">
         <v>13</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1603,8 @@
       <c r="F48" t="n">
         <v>16</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1627,8 @@
       <c r="F49" t="n">
         <v>28</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1651,8 @@
       <c r="F50" t="n">
         <v>32</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1675,8 @@
       <c r="F51" t="n">
         <v>14</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1573,13 +1691,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="F52" t="n">
-        <v>130</v>
+        <v>16</v>
+      </c>
+      <c r="G52" t="n">
+        <v>127</v>
+      </c>
+      <c r="H52" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -1603,6 +1727,8 @@
       <c r="F53" t="n">
         <v>16</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1751,8 @@
       <c r="F54" t="n">
         <v>32</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1775,8 @@
       <c r="F55" t="n">
         <v>14</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1799,8 @@
       <c r="F56" t="n">
         <v>28</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1823,8 @@
       <c r="F57" t="n">
         <v>28</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1847,8 @@
       <c r="F58" t="n">
         <v>23</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1871,8 @@
       <c r="F59" t="n">
         <v>28</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1895,8 @@
       <c r="F60" t="n">
         <v>28</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1919,8 @@
       <c r="F61" t="n">
         <v>57</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1793,13 +1935,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F62" t="n">
-        <v>118</v>
+        <v>15</v>
+      </c>
+      <c r="G62" t="n">
+        <v>103</v>
+      </c>
+      <c r="H62" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -1823,6 +1971,8 @@
       <c r="F63" t="n">
         <v>13</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +1995,8 @@
       <c r="F64" t="n">
         <v>16</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1859,12 +2011,18 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>161</v>
       </c>
       <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>68</v>
+      </c>
+      <c r="H65" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1873,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,19 +2042,21 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="n">
         <v>2</v>
       </c>
-      <c r="B67" t="n">
-        <v>15</v>
-      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>Opening</t>
@@ -1906,18 +2066,20 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>1</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,18 +2090,20 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>1</v>
       </c>
       <c r="B69" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,33 +2114,13 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" t="n">
-        <v>8</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>124</v>
-      </c>
-      <c r="F70" t="n">
         <v>59</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
